--- a/forms/trg/Formulir_TRG_victory.xlsx
+++ b/forms/trg/Formulir_TRG_victory.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>M. Aris Munandar</t>
+          <t>Dr. Nur Azisa, S.H., M.H.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Health Law and Criminal Law</t>
+          <t>Victimologi, Criminal Law, Restorative Justice</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -950,7 +946,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Audyna Mayasari Muin, S.H., M.H., CLA., MAP.</t>
+          <t>M. Aris Munandar</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -965,7 +961,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Criminal Law</t>
+          <t>Health Law and Criminal Law</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,7 +983,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr Haeranah, S.H., M.H.</t>
+          <t>Dr. Audyna Mayasari Muin, S.H., M.H., CLA., MAP.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1002,7 +998,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Prosedural Criminal Law</t>
+          <t>Criminal Law</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,7 +1020,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Hijrah Adhiyanti Mirzana, S.H., M.H.</t>
+          <t>Dr Haeranah, S.H., M.H.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1039,7 +1035,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Penologi</t>
+          <t>Prosedural Criminal Law</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,22 +1057,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Mutawalli Mukhlis, S.H., M.H.</t>
+          <t>Dr. Hijrah Adhiyanti Mirzana, S.H., M.H.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Sekolah Tinggi Agama Islam Negeri Majene: Majene, West Sulawesi</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Constitutional Law, Political Party Law, Environmental Law</t>
+          <t>Penologi</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,22 +1094,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Associate Prof. Dr. Aspalella A. Rahman</t>
+          <t>Dr. Muhammad Mutawalli Mukhlis, S.H., M.H.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Universitas Utara Malaysia</t>
+          <t>Sekolah Tinggi Agama Islam Negeri Majene: Majene, West Sulawesi</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>riminal law and anti money laundering law</t>
+          <t>Constitutional Law, Political Party Law, Environmental Law</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1135,22 +1131,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Associate Paul Atagamen Aidonojie, Ph.D.</t>
+          <t>Associate Prof. Dr. Aspalella A. Rahman</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Kampala International University</t>
+          <t>Universitas Utara Malaysia</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>TECH AND CYBER LAW, ENVIRONMENTAL LAW, HUMAN RIGHTS LAW, REVENUE LAW, AND MEDICAL LAW.</t>
+          <t>riminal law and anti money laundering law</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1172,22 +1168,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Afif Muhni, S.H., M.H.</t>
+          <t>Associate Paul Atagamen Aidonojie, Ph.D.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Kampala International University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Criminal Law</t>
+          <t>TECH AND CYBER LAW, ENVIRONMENTAL LAW, HUMAN RIGHTS LAW, REVENUE LAW, AND MEDICAL LAW.</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,7 +1205,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Ismail Iskandar, S.H., M.H.</t>
+          <t>Afif Muhni, S.H., M.H.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1246,7 +1242,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Syarif Saddam Rivanie Parawansa, S.H., M.H.</t>
+          <t>Ismail Iskandar, S.H., M.H.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1283,12 +1279,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Ardiansah Akbar, S.H. M.H.</t>
+          <t>Dr. Syarif Saddam Rivanie Parawansa, S.H., M.H.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1320,7 +1316,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Andi Dewi Pratiwi, S.H. M.H.</t>
+          <t>Ardiansah Akbar, S.H. M.H.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1357,7 +1353,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Nur Amelinda Kharia, S.H.</t>
+          <t>Andi Dewi Pratiwi, S.H. M.H.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1372,7 +1368,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Victimologi and Criminal Law</t>
+          <t>Criminal Law</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1392,10 +1388,26 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Nur Amelinda Kharia, S.H.</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Victimologi and Criminal Law</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1403,7 +1415,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1592,15 +1608,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
